--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_25.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_25.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>InformationLevel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>DV</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.146283414915007</v>
+        <v>1.561161171715113</v>
       </c>
       <c r="C2">
-        <v>0.2867570324876625</v>
+        <v>-0.06991013961257098</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3246960160317177</v>
+        <v>0.3331293472491954</v>
       </c>
       <c r="C3">
-        <v>0.0897279779942774</v>
+        <v>-0.3064275013602744</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.01249976345915709</v>
+        <v>0.22126273190272</v>
       </c>
       <c r="C4">
-        <v>-1.916019236205585</v>
+        <v>2.007034909299205</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1765404642336092</v>
+        <v>-0.02085348640518895</v>
       </c>
       <c r="C5">
-        <v>1.434524614277464</v>
+        <v>-0.2985754717221519</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-2.219296294341497</v>
+        <v>-0.734160583509389</v>
       </c>
       <c r="C6">
-        <v>-1.009736559907507</v>
+        <v>0.6764535499511212</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.02521320425969639</v>
+        <v>-0.7924576554979181</v>
       </c>
       <c r="C7">
-        <v>0.9928936487335014</v>
+        <v>-0.867303347486298</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.5103351799533248</v>
+        <v>-0.3473855049008924</v>
       </c>
       <c r="C8">
-        <v>0.5668984873458076</v>
+        <v>1.075490888489073</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.4417178461478623</v>
+        <v>0.2155737619448396</v>
       </c>
       <c r="C9">
-        <v>-1.009213791128429</v>
+        <v>-1.504096601507954</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.454889327929709</v>
+        <v>0.6723953178845558</v>
       </c>
       <c r="C10">
-        <v>-1.104840436867558</v>
+        <v>0.08430307329454492</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.713018996285615</v>
+        <v>0.003091592793407834</v>
       </c>
       <c r="C11">
-        <v>1.115815974182769</v>
+        <v>1.00208851439529</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.05680905111429467</v>
+        <v>-0.4986037216041566</v>
       </c>
       <c r="C12">
-        <v>-0.7570863451518144</v>
+        <v>-1.390266104902814</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-1.466205936992702</v>
+        <v>2.115946545838602</v>
       </c>
       <c r="C13">
-        <v>-1.314134877465576</v>
+        <v>1.503768020585844</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9991284530135112</v>
+        <v>-0.07828512826167471</v>
       </c>
       <c r="C14">
-        <v>1.20181298741756</v>
+        <v>0.1803326946469603</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.2461251476380471</v>
+        <v>-1.214543163554452</v>
       </c>
       <c r="C15">
-        <v>-1.334580690915008</v>
+        <v>-1.607392113015433</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.8101986512083099</v>
+        <v>0.1355521389585262</v>
       </c>
       <c r="C16">
-        <v>0.7100887088141533</v>
+        <v>-0.05992600362618351</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.7244490462060104</v>
+        <v>1.452551999189617</v>
       </c>
       <c r="C17">
-        <v>0.6309496513434317</v>
+        <v>-1.034917881140643</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.1440551047582024</v>
+        <v>-0.2610367512788451</v>
       </c>
       <c r="C18">
-        <v>0.8558527295160751</v>
+        <v>0.5279167331354341</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.2007466953441489</v>
+        <v>-0.01924618602332344</v>
       </c>
       <c r="C19">
-        <v>-0.05561405296514314</v>
+        <v>1.266361161855175</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.2175478927815371</v>
+        <v>-0.4112515039415877</v>
       </c>
       <c r="C20">
-        <v>2.03891837580045</v>
+        <v>-0.8673535860277913</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.272152419421694</v>
+        <v>1.169357554299542</v>
       </c>
       <c r="C21">
-        <v>-1.347963010380945</v>
+        <v>2.06001758074366</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.825523704314414</v>
+        <v>-0.3755124665103025</v>
       </c>
       <c r="C22">
-        <v>-1.770250573495883</v>
+        <v>-0.7872506718692636</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.2685299854722343</v>
+        <v>1.215440796067623</v>
       </c>
       <c r="C23">
-        <v>-1.352189701142977</v>
+        <v>-1.167338672406627</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.106084903859373</v>
+        <v>1.191439855015592</v>
       </c>
       <c r="C24">
-        <v>0.7659475102882602</v>
+        <v>0.9703790433208976</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.02123396178369683</v>
+        <v>0.2488701273428497</v>
       </c>
       <c r="C25">
-        <v>0.4066718412031196</v>
+        <v>-1.90511769652682</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.01715292307430031</v>
+        <v>0.2731889465520331</v>
       </c>
       <c r="C26">
-        <v>1.214558838372993</v>
+        <v>1.265720532502979</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.367320255567725</v>
+        <v>1.397561128879185</v>
       </c>
       <c r="C27">
-        <v>0.6177216519501429</v>
+        <v>1.271661617289852</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.1293512084115326</v>
+        <v>1.265240381780569</v>
       </c>
       <c r="C28">
-        <v>1.424451462327931</v>
+        <v>1.235475729474294</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.3512932717971373</v>
+        <v>-0.6700223790122437</v>
       </c>
       <c r="C29">
-        <v>-0.5111529424092802</v>
+        <v>0.01059461197554945</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.9351573798010485</v>
+        <v>-0.2232737722780953</v>
       </c>
       <c r="C30">
-        <v>-0.8552837481114777</v>
+        <v>0.6914218732594513</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4419021552822484</v>
+        <v>0.1408678121164321</v>
       </c>
       <c r="C31">
-        <v>-0.8968897279769819</v>
+        <v>-0.6439471967836966</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.24429998648402</v>
+        <v>1.332204919976178</v>
       </c>
       <c r="C32">
-        <v>0.02113828281005697</v>
+        <v>0.4437706860074407</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.3307106068442399</v>
+        <v>-0.3495372088438706</v>
       </c>
       <c r="C33">
-        <v>1.088630494733095</v>
+        <v>0.504484608195225</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.824608324936342</v>
+        <v>-0.3552966598405252</v>
       </c>
       <c r="C34">
-        <v>0.9953718511542868</v>
+        <v>-1.037788831333882</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.7587025749826989</v>
+        <v>0.2963058485925393</v>
       </c>
       <c r="C35">
-        <v>1.354578171687618</v>
+        <v>1.121240068949957</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-1.556317733371692</v>
+        <v>0.09403342158045</v>
       </c>
       <c r="C36">
-        <v>-2.489847444342465</v>
+        <v>0.9653981844133708</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.06142862455131108</v>
+        <v>1.566079378359587</v>
       </c>
       <c r="C37">
-        <v>0.01082046353206965</v>
+        <v>0.747383820525212</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.5201026205136421</v>
+        <v>-0.2100313833332072</v>
       </c>
       <c r="C38">
-        <v>0.994439280823995</v>
+        <v>-1.062571588657609</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.6158550896298861</v>
+        <v>-1.420107410406775</v>
       </c>
       <c r="C39">
-        <v>-0.8965282397480748</v>
+        <v>-0.8375045277753246</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.8091177396844562</v>
+        <v>0.5460833426244733</v>
       </c>
       <c r="C40">
-        <v>1.233492335859436</v>
+        <v>0.5508860551985932</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.7788705966794643</v>
+        <v>1.618432367856896</v>
       </c>
       <c r="C41">
-        <v>0.2883755113261384</v>
+        <v>-0.8763749512521257</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.3249029347698737</v>
+        <v>0.2398807203649043</v>
       </c>
       <c r="C42">
-        <v>-0.8961145687383306</v>
+        <v>1.269397476485594</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.4504961861394254</v>
+        <v>-1.737262519602116</v>
       </c>
       <c r="C43">
-        <v>0.09794302852344362</v>
+        <v>-0.6158382131947575</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.9009098571445181</v>
+        <v>-0.2495092123200297</v>
       </c>
       <c r="C44">
-        <v>0.237508538947018</v>
+        <v>1.079442436111195</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.006281655558325221</v>
+        <v>0.05614643051273303</v>
       </c>
       <c r="C45">
-        <v>0.2740028908844547</v>
+        <v>-0.7387721688552915</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.1959941140019198</v>
+        <v>0.008505607858822897</v>
       </c>
       <c r="C46">
-        <v>0.6477840653463358</v>
+        <v>0.02645888789821231</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.5697891676341091</v>
+        <v>-0.3171829049437248</v>
       </c>
       <c r="C47">
-        <v>-0.5688596587461479</v>
+        <v>-0.05549570541512765</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-2.124087949934684</v>
+        <v>-0.6623448682749398</v>
       </c>
       <c r="C48">
-        <v>-1.49067768439758</v>
+        <v>-1.048177447352168</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.04824570452954243</v>
+        <v>-1.650558802666969</v>
       </c>
       <c r="C49">
-        <v>-0.3119224356472469</v>
+        <v>-0.4896900767047833</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.1482422876044889</v>
+        <v>-0.838440603198041</v>
       </c>
       <c r="C50">
-        <v>0.8454918679643217</v>
+        <v>0.5956266377709081</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.08255464951336013</v>
+        <v>0.5837167638838563</v>
       </c>
       <c r="C51">
-        <v>-0.4125216582070164</v>
+        <v>0.2615160438503898</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.03600569930654522</v>
+      </c>
+      <c r="C52">
+        <v>-0.4261070757442272</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>0.1721320468957434</v>
+      </c>
+      <c r="C53">
+        <v>-0.6972143910558537</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-1.302146809209708</v>
+      </c>
+      <c r="C54">
+        <v>-1.680543005176643</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.9537940887976011</v>
+      </c>
+      <c r="C55">
+        <v>-0.4589935654771279</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-0.7859747891518652</v>
+      </c>
+      <c r="C56">
+        <v>1.763483127630228</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-0.601315486781975</v>
+      </c>
+      <c r="C57">
+        <v>-1.859533738043167</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-0.04649241295809735</v>
+      </c>
+      <c r="C58">
+        <v>0.715949809315226</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>-0.381739927376635</v>
+      </c>
+      <c r="C59">
+        <v>-0.5329108526593915</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-0.8560697738298788</v>
+      </c>
+      <c r="C60">
+        <v>1.502306165657659</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.5416197407216263</v>
+      </c>
+      <c r="C61">
+        <v>-0.7201998254420764</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-1.095176433881705</v>
+      </c>
+      <c r="C62">
+        <v>0.1866784172821627</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>-1.439790348562367</v>
+      </c>
+      <c r="C63">
+        <v>-0.1093878221075069</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>0.6271126459527639</v>
+      </c>
+      <c r="C64">
+        <v>0.3244503346703169</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.1480521882715776</v>
+      </c>
+      <c r="C65">
+        <v>-0.04704668674400687</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-1.079744024132464</v>
+      </c>
+      <c r="C66">
+        <v>0.1335834878846727</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>-0.7669605458173426</v>
+      </c>
+      <c r="C67">
+        <v>-0.2674834464915912</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>0.225052515008293</v>
+      </c>
+      <c r="C68">
+        <v>0.8839859008715694</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-1.201078796419428</v>
+      </c>
+      <c r="C69">
+        <v>-0.2897833929697743</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>2.183817967972974</v>
+      </c>
+      <c r="C70">
+        <v>1.396660957161205</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-1.566226820939004</v>
+      </c>
+      <c r="C71">
+        <v>-0.6339760474179564</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>-0.1315644517334295</v>
+      </c>
+      <c r="C72">
+        <v>-1.078729937661518</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-0.6464270878986155</v>
+      </c>
+      <c r="C73">
+        <v>-1.444528966009997</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>-0.2651590731924263</v>
+      </c>
+      <c r="C74">
+        <v>0.0929877820095988</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>0.6049252882832243</v>
+      </c>
+      <c r="C75">
+        <v>0.7086643474293923</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>1.194862298146979</v>
+      </c>
+      <c r="C76">
+        <v>-0.5014320388665356</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.1645417643531218</v>
+      </c>
+      <c r="C77">
+        <v>0.03112145294693888</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>0.4440281767702082</v>
+      </c>
+      <c r="C78">
+        <v>-0.2116753082487974</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-0.3030870462994769</v>
+      </c>
+      <c r="C79">
+        <v>-0.3074621827009842</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-0.5617568451005487</v>
+      </c>
+      <c r="C80">
+        <v>-0.2498655908341857</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.8133424163585247</v>
+      </c>
+      <c r="C81">
+        <v>-1.99700300691397</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>2.167686877203702</v>
+      </c>
+      <c r="C82">
+        <v>1.570028719716551</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>-0.3209017886687488</v>
+      </c>
+      <c r="C83">
+        <v>-0.2001766778503406</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.6865832119104112</v>
+      </c>
+      <c r="C84">
+        <v>-0.1820843882986934</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-1.008433052112003</v>
+      </c>
+      <c r="C85">
+        <v>-1.04930763811388</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-0.2262309381080254</v>
+      </c>
+      <c r="C86">
+        <v>-0.3905413057256085</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-0.8528725912604785</v>
+      </c>
+      <c r="C87">
+        <v>-0.633895240499053</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-0.4455538715845515</v>
+      </c>
+      <c r="C88">
+        <v>-1.045105577178533</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>0.1556799070244694</v>
+      </c>
+      <c r="C89">
+        <v>0.2293675998917317</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.9864847526684384</v>
+      </c>
+      <c r="C90">
+        <v>0.2517501166113114</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-0.03844201133669169</v>
+      </c>
+      <c r="C91">
+        <v>1.323985909444123</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>-0.07882996705756429</v>
+      </c>
+      <c r="C92">
+        <v>-1.363696118993217</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>-1.122025389224788</v>
+      </c>
+      <c r="C93">
+        <v>0.6825762976012074</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>-1.968943367058452</v>
+      </c>
+      <c r="C94">
+        <v>-0.785026639756097</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>0.697480604503682</v>
+      </c>
+      <c r="C95">
+        <v>0.06180140510260076</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>0.5867427704751507</v>
+      </c>
+      <c r="C96">
+        <v>1.263705175507039</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>-0.01349509783244906</v>
+      </c>
+      <c r="C97">
+        <v>0.667823704744446</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-0.06612260589497382</v>
+      </c>
+      <c r="C98">
+        <v>-0.4614007865236423</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>0.2776427871943937</v>
+      </c>
+      <c r="C99">
+        <v>-1.722850712239049</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>0.5411028272733621</v>
+      </c>
+      <c r="C100">
+        <v>1.518625916844873</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>-0.1655141129313056</v>
+      </c>
+      <c r="C101">
+        <v>-0.7535692818728492</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-0.7582575576861704</v>
+      </c>
+      <c r="C102">
+        <v>-0.07698982036188831</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.228214261720902</v>
+      </c>
+      <c r="C103">
+        <v>-0.7875777756260602</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-1.388220139850368</v>
+      </c>
+      <c r="C104">
+        <v>-0.6040952601256496</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-1.46763316632101</v>
+      </c>
+      <c r="C105">
+        <v>-2.46362117457859</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-1.129690486550917</v>
+      </c>
+      <c r="C106">
+        <v>-1.022137974897462</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-2.100563273494152</v>
+      </c>
+      <c r="C107">
+        <v>-1.489013160482644</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.8932473175123391</v>
+      </c>
+      <c r="C108">
+        <v>-0.4036489009058963</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.01170352113877521</v>
+      </c>
+      <c r="C109">
+        <v>0.03081772497238906</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.873905703660422</v>
+      </c>
+      <c r="C110">
+        <v>0.0597285466739878</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-0.4158856194356783</v>
+      </c>
+      <c r="C111">
+        <v>-0.6386472256856064</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.572856864855711</v>
+      </c>
+      <c r="C112">
+        <v>-2.157999923529907</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.3485947974740636</v>
+      </c>
+      <c r="C113">
+        <v>-0.3481371367958088</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>0.5678565168527953</v>
+      </c>
+      <c r="C114">
+        <v>0.04720846808278326</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.9127130858186479</v>
+      </c>
+      <c r="C115">
+        <v>-1.034668012785454</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-1.468837392926212</v>
+      </c>
+      <c r="C116">
+        <v>-0.4330654844439752</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>0.3813680420387163</v>
+      </c>
+      <c r="C117">
+        <v>0.07128295984561153</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.4752573117925487</v>
+      </c>
+      <c r="C118">
+        <v>-0.9322233909393018</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.754007923866532</v>
+      </c>
+      <c r="C119">
+        <v>0.2937481454188969</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1.46624423763407</v>
+      </c>
+      <c r="C120">
+        <v>-1.183732554099346</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.9053033361076516</v>
+      </c>
+      <c r="C121">
+        <v>-0.2275669850936113</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.5937707223058151</v>
+      </c>
+      <c r="C122">
+        <v>-0.1958724436987066</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.2679285721368619</v>
+      </c>
+      <c r="C123">
+        <v>0.2268639163488713</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-1.174839414821457</v>
+      </c>
+      <c r="C124">
+        <v>-0.4199588783781549</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.4272038006352074</v>
+      </c>
+      <c r="C125">
+        <v>-0.1410956303157985</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-1.3670536408116</v>
+      </c>
+      <c r="C126">
+        <v>-1.442395021975056</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.8544263525142822</v>
+      </c>
+      <c r="C127">
+        <v>0.2311985548494975</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.8667426692158816</v>
+      </c>
+      <c r="C128">
+        <v>-0.2329833959877218</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.1242130320745062</v>
+      </c>
+      <c r="C129">
+        <v>0.2777212544284213</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>0.457519940294507</v>
+      </c>
+      <c r="C130">
+        <v>-0.4470035855465719</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>1.029786695533781</v>
+      </c>
+      <c r="C131">
+        <v>1.206571325804694</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.3800747238833073</v>
+      </c>
+      <c r="C132">
+        <v>0.658550315824157</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>0.7757581476779286</v>
+      </c>
+      <c r="C133">
+        <v>-0.5214085023062414</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-0.4699549834456025</v>
+      </c>
+      <c r="C134">
+        <v>0.106476162524097</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.9809931715604381</v>
+      </c>
+      <c r="C135">
+        <v>-0.8476675589988916</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-1.222077552518343</v>
+      </c>
+      <c r="C136">
+        <v>0.4269130269473846</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>3.341547163969681</v>
+      </c>
+      <c r="C137">
+        <v>1.358799102414972</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.7910788163383836</v>
+      </c>
+      <c r="C138">
+        <v>-1.053505807781199</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>-1.417666495166406</v>
+      </c>
+      <c r="C139">
+        <v>-0.5995886859568293</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>0.4338716753643532</v>
+      </c>
+      <c r="C140">
+        <v>-1.960012606584806</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.307605786864532</v>
+      </c>
+      <c r="C141">
+        <v>0.3381717152454685</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-0.8186120470210732</v>
+      </c>
+      <c r="C142">
+        <v>-0.165803605040639</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0.0001413514390576714</v>
+      </c>
+      <c r="C143">
+        <v>-1.018139552011188</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.8316538973798606</v>
+      </c>
+      <c r="C144">
+        <v>0.7960127039347992</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-0.5789461567404353</v>
+      </c>
+      <c r="C145">
+        <v>-0.1010798552602319</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.4446727436550497</v>
+      </c>
+      <c r="C146">
+        <v>-0.4988077680272442</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.7954746323898934</v>
+      </c>
+      <c r="C147">
+        <v>-0.118955894684654</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.4711169230579368</v>
+      </c>
+      <c r="C148">
+        <v>-0.4138958335971971</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.5170242833947954</v>
+      </c>
+      <c r="C149">
+        <v>-0.07013109037491982</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-1.082754206042932</v>
+      </c>
+      <c r="C150">
+        <v>-0.925092180741923</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.2072302824032876</v>
+      </c>
+      <c r="C151">
+        <v>3.078154124106781</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1.858168068108684</v>
+      </c>
+      <c r="C152">
+        <v>-0.5248202159179756</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>1.498057647862456</v>
+      </c>
+      <c r="C153">
+        <v>-0.07783440397999031</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>0.09846362127176558</v>
+      </c>
+      <c r="C154">
+        <v>0.4737027756995033</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-2.115154046359395</v>
+      </c>
+      <c r="C155">
+        <v>1.039653343333681</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>-1.402932252696363</v>
+      </c>
+      <c r="C156">
+        <v>-0.1410166907443851</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>0.7474665495937083</v>
+      </c>
+      <c r="C157">
+        <v>0.7103450664171771</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-0.9897503005925549</v>
+      </c>
+      <c r="C158">
+        <v>-0.6614220462516138</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.737343793403708</v>
+      </c>
+      <c r="C159">
+        <v>-0.04290276017454903</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.7744999934243733</v>
+      </c>
+      <c r="C160">
+        <v>-0.01332822472480039</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.09780106016475119</v>
+      </c>
+      <c r="C161">
+        <v>0.05100593946488403</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>0.8502964075296364</v>
+      </c>
+      <c r="C162">
+        <v>2.481989494920752</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.2006486186773502</v>
+      </c>
+      <c r="C163">
+        <v>-0.2711919196264532</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>2.194956204691914</v>
+      </c>
+      <c r="C164">
+        <v>0.5599927545393704</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0.1040433858276766</v>
+      </c>
+      <c r="C165">
+        <v>0.7094940934369895</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-1.244912187080574</v>
+      </c>
+      <c r="C166">
+        <v>-0.2215582862897681</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.04639757452003727</v>
+      </c>
+      <c r="C167">
+        <v>0.04066461013174437</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-0.5412008403808204</v>
+      </c>
+      <c r="C168">
+        <v>-0.5962762262245936</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.5375470960808664</v>
+      </c>
+      <c r="C169">
+        <v>-0.1296352752462258</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-0.8849504573321876</v>
+      </c>
+      <c r="C170">
+        <v>-0.5884669430934868</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.05466791852823898</v>
+      </c>
+      <c r="C171">
+        <v>0.2494929573781218</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>1.170141933378429</v>
+      </c>
+      <c r="C172">
+        <v>1.681411879237281</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.6641354719534496</v>
+      </c>
+      <c r="C173">
+        <v>-1.973309418914161</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1.771015329231368</v>
+      </c>
+      <c r="C174">
+        <v>-0.2160484352119179</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.3597823441255157</v>
+      </c>
+      <c r="C175">
+        <v>-0.3954955285430884</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>0.9054701738214332</v>
+      </c>
+      <c r="C176">
+        <v>0.507026784058707</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>0.2631577837246554</v>
+      </c>
+      <c r="C177">
+        <v>0.3175156366742232</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.1255454003194628</v>
+      </c>
+      <c r="C178">
+        <v>-0.8549814656844221</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.6074991783862034</v>
+      </c>
+      <c r="C179">
+        <v>0.1873632126483652</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>1.626322171477572</v>
+      </c>
+      <c r="C180">
+        <v>2.199681487105138</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-0.4673110356776096</v>
+      </c>
+      <c r="C181">
+        <v>-0.06218509805398485</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.1907258041970507</v>
+      </c>
+      <c r="C182">
+        <v>1.08366028862451</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.6422385309117207</v>
+      </c>
+      <c r="C183">
+        <v>0.3356317720667986</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>1.042976264522456</v>
+      </c>
+      <c r="C184">
+        <v>-0.5678184065542687</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-0.7090435659925142</v>
+      </c>
+      <c r="C185">
+        <v>0.7991510971405473</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.262584300028593</v>
+      </c>
+      <c r="C186">
+        <v>-0.9441599545474187</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>0.8662500111432394</v>
+      </c>
+      <c r="C187">
+        <v>-1.098678193694134</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>1.209490875613903</v>
+      </c>
+      <c r="C188">
+        <v>0.4630965420542194</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.3227150235037117</v>
+      </c>
+      <c r="C189">
+        <v>-0.7178801517774283</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>0.4599319029364825</v>
+      </c>
+      <c r="C190">
+        <v>-0.3507737915910329</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>0.4386141754164916</v>
+      </c>
+      <c r="C191">
+        <v>0.4690637936200951</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.4876865595824955</v>
+      </c>
+      <c r="C192">
+        <v>-0.6456176841547684</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.8457464000279156</v>
+      </c>
+      <c r="C193">
+        <v>1.2344109565812</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>1.146827263379139</v>
+      </c>
+      <c r="C194">
+        <v>-0.1532775401888861</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>1.080418530354251</v>
+      </c>
+      <c r="C195">
+        <v>0.9351653736067669</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>1.145073269886245</v>
+      </c>
+      <c r="C196">
+        <v>-0.9029868509492553</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-0.4943875776263069</v>
+      </c>
+      <c r="C197">
+        <v>0.1562101051361901</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.7303412885765724</v>
+      </c>
+      <c r="C198">
+        <v>-0.9651658785912753</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.4712185775975826</v>
+      </c>
+      <c r="C199">
+        <v>0.8076019404114488</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.06750571392009552</v>
+      </c>
+      <c r="C200">
+        <v>0.8462641282513569</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0.7594874652673779</v>
+      </c>
+      <c r="C201">
+        <v>-0.1861231403845283</v>
       </c>
     </row>
   </sheetData>
